--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,31 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-10</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
+    <t>Prudential Financial, Inc.</t>
+  </si>
+  <si>
     <t>American International Group, I</t>
   </si>
   <si>
     <t>MetLife, Inc.</t>
   </si>
   <si>
-    <t>Prudential Financial, Inc.</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
+    <t>PRU</t>
+  </si>
+  <si>
     <t>AIG</t>
   </si>
   <si>
     <t>MET</t>
-  </si>
-  <si>
-    <t>PRU</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>330.91</v>
+        <v>323.68</v>
       </c>
       <c r="E2">
-        <v>56.7</v>
+        <v>59.6</v>
       </c>
       <c r="F2">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>58.9</v>
+        <v>54.8</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,19 +560,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>77.03</v>
+        <v>112.41</v>
       </c>
       <c r="E3">
-        <v>44.9</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F3">
-        <v>1.14</v>
+        <v>4.23</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I3">
         <v>50</v>
@@ -581,7 +581,7 @@
         <v>46</v>
       </c>
       <c r="K3">
-        <v>53.7</v>
+        <v>49.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>78.66</v>
+        <v>76.88</v>
       </c>
       <c r="E4">
-        <v>50.1</v>
+        <v>48.5</v>
       </c>
       <c r="F4">
-        <v>2.74</v>
+        <v>-0.09</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I4">
+        <v>46</v>
+      </c>
+      <c r="J4">
         <v>50</v>
       </c>
-      <c r="J4">
-        <v>33</v>
-      </c>
       <c r="K4">
-        <v>53.7</v>
+        <v>47.8</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>111.68</v>
+        <v>78.5</v>
       </c>
       <c r="E5">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F5">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>56</v>
+      </c>
+      <c r="I5">
+        <v>46</v>
+      </c>
+      <c r="J5">
         <v>40</v>
       </c>
-      <c r="H5">
-        <v>43</v>
-      </c>
-      <c r="I5">
-        <v>33</v>
-      </c>
-      <c r="J5">
-        <v>43</v>
-      </c>
       <c r="K5">
-        <v>40.9</v>
+        <v>47.8</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -67,25 +67,25 @@
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
+    <t>MetLife, Inc.</t>
+  </si>
+  <si>
     <t>Prudential Financial, Inc.</t>
   </si>
   <si>
     <t>American International Group, I</t>
   </si>
   <si>
-    <t>MetLife, Inc.</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
+    <t>MET</t>
+  </si>
+  <si>
     <t>PRU</t>
   </si>
   <si>
     <t>AIG</t>
-  </si>
-  <si>
-    <t>MET</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,13 +513,13 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>323.68</v>
+        <v>323.6</v>
       </c>
       <c r="E2">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="F2">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -534,7 +534,7 @@
         <v>36</v>
       </c>
       <c r="K2">
-        <v>54.8</v>
+        <v>54.3</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>112.41</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="E3">
-        <v>90.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F3">
-        <v>4.23</v>
+        <v>2.03</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>50</v>
       </c>
       <c r="J3">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K3">
-        <v>49.4</v>
+        <v>51.9</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>76.88</v>
+        <v>111.68</v>
       </c>
       <c r="E4">
-        <v>48.5</v>
+        <v>90</v>
       </c>
       <c r="F4">
-        <v>-0.09</v>
+        <v>3.55</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I4">
         <v>46</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K4">
-        <v>47.8</v>
+        <v>47.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>78.5</v>
+        <v>76.42</v>
       </c>
       <c r="E5">
-        <v>70.09999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="F5">
-        <v>2.92</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I5">
+        <v>43</v>
+      </c>
+      <c r="J5">
         <v>46</v>
       </c>
-      <c r="J5">
-        <v>40</v>
-      </c>
       <c r="K5">
-        <v>47.8</v>
+        <v>43.1</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,31 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
+    <t>Prudential Financial, Inc.</t>
+  </si>
+  <si>
+    <t>American International Group, I</t>
+  </si>
+  <si>
     <t>MetLife, Inc.</t>
   </si>
   <si>
-    <t>Prudential Financial, Inc.</t>
-  </si>
-  <si>
-    <t>American International Group, I</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
+    <t>PRU</t>
+  </si>
+  <si>
+    <t>AIG</t>
+  </si>
+  <si>
     <t>MET</t>
-  </si>
-  <si>
-    <t>PRU</t>
-  </si>
-  <si>
-    <t>AIG</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>323.6</v>
+        <v>341.84</v>
       </c>
       <c r="E2">
-        <v>59.5</v>
+        <v>68</v>
       </c>
       <c r="F2">
-        <v>0.38</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K2">
-        <v>54.3</v>
+        <v>58.6</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>77.81999999999999</v>
+        <v>116.96</v>
       </c>
       <c r="E3">
-        <v>66.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F3">
-        <v>2.03</v>
+        <v>4.73</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I3">
+        <v>56</v>
+      </c>
+      <c r="J3">
         <v>50</v>
       </c>
-      <c r="J3">
-        <v>43</v>
-      </c>
       <c r="K3">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>111.68</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F4">
-        <v>3.55</v>
+        <v>10.22</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I4">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J4">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K4">
-        <v>47.3</v>
+        <v>43.4</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>76.42</v>
+        <v>82.16</v>
       </c>
       <c r="E5">
-        <v>44.5</v>
+        <v>87.2</v>
       </c>
       <c r="F5">
-        <v>-0.6899999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K5">
-        <v>43.1</v>
+        <v>40.6</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
@@ -70,22 +70,22 @@
     <t>Prudential Financial, Inc.</t>
   </si>
   <si>
+    <t>MetLife, Inc.</t>
+  </si>
+  <si>
     <t>American International Group, I</t>
   </si>
   <si>
-    <t>MetLife, Inc.</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
     <t>PRU</t>
   </si>
   <si>
+    <t>MET</t>
+  </si>
+  <si>
     <t>AIG</t>
-  </si>
-  <si>
-    <t>MET</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>341.84</v>
+        <v>331.83</v>
       </c>
       <c r="E2">
-        <v>68</v>
+        <v>53.3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>1.12</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2">
+        <v>66</v>
+      </c>
+      <c r="I2">
         <v>63</v>
       </c>
-      <c r="I2">
-        <v>66</v>
-      </c>
       <c r="J2">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K2">
-        <v>58.6</v>
+        <v>52.8</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>116.96</v>
+        <v>113.97</v>
       </c>
       <c r="E3">
-        <v>90.40000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="F3">
-        <v>4.73</v>
+        <v>-1.37</v>
       </c>
       <c r="G3">
+        <v>40</v>
+      </c>
+      <c r="H3">
         <v>50</v>
-      </c>
-      <c r="H3">
-        <v>53</v>
       </c>
       <c r="I3">
         <v>56</v>
       </c>
       <c r="J3">
+        <v>56</v>
+      </c>
+      <c r="K3">
         <v>50</v>
-      </c>
-      <c r="K3">
-        <v>51.6</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>84.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="E4">
-        <v>85</v>
+        <v>59.2</v>
       </c>
       <c r="F4">
-        <v>10.22</v>
+        <v>-1.73</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I4">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K4">
-        <v>43.4</v>
+        <v>46</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>82.16</v>
+        <v>86.48</v>
       </c>
       <c r="E5">
-        <v>87.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F5">
-        <v>4.45</v>
+        <v>0.34</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
         <v>36</v>
       </c>
-      <c r="J5">
-        <v>33</v>
-      </c>
       <c r="K5">
-        <v>40.6</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,31 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
+    <t>American International Group, I</t>
+  </si>
+  <si>
     <t>Prudential Financial, Inc.</t>
   </si>
   <si>
     <t>MetLife, Inc.</t>
   </si>
   <si>
-    <t>American International Group, I</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
+    <t>AIG</t>
+  </si>
+  <si>
     <t>PRU</t>
   </si>
   <si>
     <t>MET</t>
-  </si>
-  <si>
-    <t>AIG</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>331.83</v>
+        <v>336.4</v>
       </c>
       <c r="E2">
-        <v>53.3</v>
+        <v>49.6</v>
       </c>
       <c r="F2">
-        <v>1.12</v>
+        <v>2.69</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I2">
         <v>63</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>52.8</v>
+        <v>55.7</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>113.97</v>
+        <v>84.27</v>
       </c>
       <c r="E3">
-        <v>60.3</v>
+        <v>59.8</v>
       </c>
       <c r="F3">
-        <v>-1.37</v>
+        <v>-2.6</v>
       </c>
       <c r="G3">
         <v>40</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K3">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>80.3</v>
+        <v>113.87</v>
       </c>
       <c r="E4">
-        <v>59.2</v>
+        <v>29.9</v>
       </c>
       <c r="F4">
-        <v>-1.73</v>
+        <v>-0.59</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="K4">
-        <v>46</v>
+        <v>36.7</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>86.48</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E5">
-        <v>84.09999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="F5">
-        <v>0.34</v>
+        <v>-0.9</v>
       </c>
       <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>56</v>
+      </c>
+      <c r="I5">
         <v>50</v>
       </c>
-      <c r="H5">
-        <v>30</v>
-      </c>
-      <c r="I5">
-        <v>26</v>
-      </c>
       <c r="J5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K5">
-        <v>41</v>
+        <v>35.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,31 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
+    <t>Prudential Financial, Inc.</t>
+  </si>
+  <si>
+    <t>MetLife, Inc.</t>
+  </si>
+  <si>
     <t>American International Group, I</t>
   </si>
   <si>
-    <t>Prudential Financial, Inc.</t>
-  </si>
-  <si>
-    <t>MetLife, Inc.</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
+    <t>PRU</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
     <t>AIG</t>
-  </si>
-  <si>
-    <t>PRU</t>
-  </si>
-  <si>
-    <t>MET</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,16 +513,16 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>336.4</v>
+        <v>348.97</v>
       </c>
       <c r="E2">
-        <v>49.6</v>
+        <v>57.8</v>
       </c>
       <c r="F2">
-        <v>2.69</v>
+        <v>6.09</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>63</v>
@@ -531,10 +531,10 @@
         <v>63</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K2">
-        <v>55.7</v>
+        <v>53.7</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>84.27</v>
+        <v>117.67</v>
       </c>
       <c r="E3">
-        <v>59.8</v>
+        <v>50.3</v>
       </c>
       <c r="F3">
-        <v>-2.6</v>
+        <v>3.83</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>42.9</v>
+        <v>50.9</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>113.87</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="E4">
-        <v>29.9</v>
+        <v>40.9</v>
       </c>
       <c r="F4">
-        <v>-0.59</v>
+        <v>1.49</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="K4">
-        <v>36.7</v>
+        <v>47.9</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>80.31999999999999</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="E5">
-        <v>34.9</v>
+        <v>18.7</v>
       </c>
       <c r="F5">
-        <v>-0.9</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="G5">
         <v>10</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K5">
-        <v>35.5</v>
+        <v>30.9</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -534,7 +534,7 @@
         <v>33</v>
       </c>
       <c r="K2">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -581,7 +581,7 @@
         <v>53</v>
       </c>
       <c r="K3">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -628,7 +628,7 @@
         <v>33</v>
       </c>
       <c r="K4">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>43</v>
       </c>
       <c r="K5">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>348.97</v>
+        <v>341.7</v>
       </c>
       <c r="E2">
-        <v>57.8</v>
+        <v>57.4</v>
       </c>
       <c r="F2">
-        <v>6.09</v>
+        <v>2.87</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I2">
         <v>63</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K2">
-        <v>53.8</v>
+        <v>56.3</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>117.67</v>
+        <v>116.85</v>
       </c>
       <c r="E3">
-        <v>50.3</v>
+        <v>49</v>
       </c>
       <c r="F3">
-        <v>3.83</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I3">
         <v>56</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>81.18000000000001</v>
+        <v>78.27</v>
       </c>
       <c r="E4">
-        <v>40.9</v>
+        <v>30.8</v>
       </c>
       <c r="F4">
-        <v>1.49</v>
+        <v>-1.89</v>
       </c>
       <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>56</v>
+      </c>
+      <c r="I4">
+        <v>53</v>
+      </c>
+      <c r="J4">
         <v>40</v>
       </c>
-      <c r="H4">
-        <v>50</v>
-      </c>
-      <c r="I4">
-        <v>56</v>
-      </c>
-      <c r="J4">
-        <v>33</v>
-      </c>
       <c r="K4">
-        <v>48</v>
+        <v>37.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>78.06999999999999</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="E5">
-        <v>18.7</v>
+        <v>19.2</v>
       </c>
       <c r="F5">
-        <v>-9.720000000000001</v>
+        <v>-10.52</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>50</v>
       </c>
       <c r="I5">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>31</v>
+        <v>30.3</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>341.7</v>
+        <v>343.98</v>
       </c>
       <c r="E2">
-        <v>57.4</v>
+        <v>65</v>
       </c>
       <c r="F2">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
+        <v>53</v>
+      </c>
+      <c r="I2">
         <v>60</v>
       </c>
-      <c r="I2">
-        <v>63</v>
-      </c>
       <c r="J2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K2">
-        <v>56.3</v>
+        <v>57.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>116.85</v>
+        <v>118.08</v>
       </c>
       <c r="E3">
-        <v>49</v>
+        <v>60.3</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>78.27</v>
+        <v>79.41</v>
       </c>
       <c r="E4">
-        <v>30.8</v>
+        <v>39.8</v>
       </c>
       <c r="F4">
-        <v>-1.89</v>
+        <v>-1.13</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I4">
         <v>53</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K4">
-        <v>37.3</v>
+        <v>39.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>77.06999999999999</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="E5">
-        <v>19.2</v>
+        <v>10.9</v>
       </c>
       <c r="F5">
-        <v>-10.52</v>
+        <v>-10.49</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K5">
-        <v>30.3</v>
+        <v>33.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -534,7 +534,7 @@
         <v>26</v>
       </c>
       <c r="K2">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -581,7 +581,7 @@
         <v>53</v>
       </c>
       <c r="K3">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -628,7 +628,7 @@
         <v>36</v>
       </c>
       <c r="K4">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>53</v>
       </c>
       <c r="K5">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>343.98</v>
+        <v>340.51</v>
       </c>
       <c r="E2">
-        <v>65</v>
+        <v>61.8</v>
       </c>
       <c r="F2">
-        <v>2.25</v>
+        <v>-0.44</v>
       </c>
       <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
         <v>60</v>
       </c>
-      <c r="H2">
-        <v>53</v>
-      </c>
       <c r="I2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="K2">
-        <v>57.2</v>
+        <v>55.8</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>118.08</v>
+        <v>117.74</v>
       </c>
       <c r="E3">
-        <v>60.3</v>
+        <v>61.4</v>
       </c>
       <c r="F3">
-        <v>3.7</v>
+        <v>0.32</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>79.41</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="E4">
-        <v>39.8</v>
+        <v>36.7</v>
       </c>
       <c r="F4">
-        <v>-1.13</v>
+        <v>-4.22</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <v>53</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K4">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>75.43000000000001</v>
+        <v>74.09</v>
       </c>
       <c r="E5">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>-10.49</v>
+        <v>-12.19</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J5">
         <v>53</v>
       </c>
       <c r="K5">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>340.51</v>
+        <v>333.93</v>
       </c>
       <c r="E2">
-        <v>61.8</v>
+        <v>57.3</v>
       </c>
       <c r="F2">
-        <v>-0.44</v>
+        <v>-4.31</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I2">
         <v>66</v>
       </c>
       <c r="J2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K2">
-        <v>55.8</v>
+        <v>51.3</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>117.74</v>
+        <v>116.58</v>
       </c>
       <c r="E3">
-        <v>61.4</v>
+        <v>56.7</v>
       </c>
       <c r="F3">
-        <v>0.32</v>
+        <v>-0.93</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I3">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>50.8</v>
+        <v>39.3</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>78.31999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="E4">
-        <v>36.7</v>
+        <v>33.9</v>
       </c>
       <c r="F4">
-        <v>-4.22</v>
+        <v>-5.05</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I4">
         <v>53</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K4">
-        <v>38.6</v>
+        <v>34.1</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>74.09</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="F5">
-        <v>-12.19</v>
+        <v>-7.4</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J5">
         <v>53</v>
       </c>
       <c r="K5">
-        <v>34.4</v>
+        <v>30.1</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,25 +61,25 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>Prudential Financial, Inc.</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
-    <t>Prudential Financial, Inc.</t>
-  </si>
-  <si>
     <t>MetLife, Inc.</t>
   </si>
   <si>
     <t>American International Group, I</t>
   </si>
   <si>
+    <t>PRU</t>
+  </si>
+  <si>
     <t>UNH</t>
-  </si>
-  <si>
-    <t>PRU</t>
   </si>
   <si>
     <t>MET</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>333.93</v>
+        <v>111.69</v>
       </c>
       <c r="E2">
-        <v>57.3</v>
+        <v>43.9</v>
       </c>
       <c r="F2">
-        <v>-4.31</v>
+        <v>-5.41</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>51.3</v>
+        <v>45.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>116.58</v>
+        <v>331.02</v>
       </c>
       <c r="E3">
-        <v>56.7</v>
+        <v>49.4</v>
       </c>
       <c r="F3">
-        <v>-0.93</v>
+        <v>-3.77</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="K3">
-        <v>39.3</v>
+        <v>43.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>77.08</v>
+        <v>76.77</v>
       </c>
       <c r="E4">
-        <v>33.9</v>
+        <v>38.5</v>
       </c>
       <c r="F4">
-        <v>-5.05</v>
+        <v>-3.32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>46</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K4">
-        <v>34.1</v>
+        <v>35.1</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>72.29000000000001</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="E5">
-        <v>6.7</v>
+        <v>14.2</v>
       </c>
       <c r="F5">
-        <v>-7.4</v>
+        <v>-3.31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I5">
         <v>43</v>
       </c>
       <c r="J5">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>30.1</v>
+        <v>32.3</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
   </si>
   <si>
     <t>Prudential Financial, Inc.</t>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,40 +61,40 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>UnitedHealth Group Incorporated</t>
+  </si>
+  <si>
+    <t>American International Group, I</t>
   </si>
   <si>
     <t>Prudential Financial, Inc.</t>
   </si>
   <si>
-    <t>UnitedHealth Group Incorporated</t>
-  </si>
-  <si>
     <t>MetLife, Inc.</t>
   </si>
   <si>
-    <t>American International Group, I</t>
+    <t>UNH</t>
+  </si>
+  <si>
+    <t>AIG</t>
   </si>
   <si>
     <t>PRU</t>
   </si>
   <si>
-    <t>UNH</t>
-  </si>
-  <si>
     <t>MET</t>
   </si>
   <si>
-    <t>AIG</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>111.69</v>
+        <v>294.93</v>
       </c>
       <c r="E2">
-        <v>43.9</v>
+        <v>64.5</v>
       </c>
       <c r="F2">
-        <v>-5.41</v>
+        <v>4.46</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="K2">
-        <v>45.1</v>
+        <v>41.3</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>331.02</v>
+        <v>81.12</v>
       </c>
       <c r="E3">
-        <v>49.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F3">
-        <v>-3.77</v>
+        <v>1.43</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>43.5</v>
+        <v>35.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>76.77</v>
+        <v>99.95</v>
       </c>
       <c r="E4">
-        <v>38.5</v>
+        <v>47.6</v>
       </c>
       <c r="F4">
-        <v>-3.32</v>
+        <v>-0.92</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="K4">
-        <v>35.1</v>
+        <v>34.5</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>72.93000000000001</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="E5">
-        <v>14.2</v>
+        <v>41.5</v>
       </c>
       <c r="F5">
-        <v>-3.31</v>
+        <v>-2.66</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I5">
+        <v>53</v>
+      </c>
+      <c r="J5">
         <v>43</v>
       </c>
-      <c r="J5">
-        <v>46</v>
-      </c>
       <c r="K5">
-        <v>32.3</v>
+        <v>33.3</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,31 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
+    <t>MetLife, Inc.</t>
+  </si>
+  <si>
     <t>American International Group, I</t>
   </si>
   <si>
     <t>Prudential Financial, Inc.</t>
   </si>
   <si>
-    <t>MetLife, Inc.</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
+    <t>MET</t>
+  </si>
+  <si>
     <t>AIG</t>
   </si>
   <si>
     <t>PRU</t>
-  </si>
-  <si>
-    <t>MET</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>294.93</v>
+        <v>286.48</v>
       </c>
       <c r="E2">
-        <v>64.5</v>
+        <v>44.2</v>
       </c>
       <c r="F2">
-        <v>4.46</v>
+        <v>-2.32</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I2">
         <v>43</v>
       </c>
       <c r="J2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K2">
-        <v>41.3</v>
+        <v>33.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>81.12</v>
+        <v>71.83</v>
       </c>
       <c r="E3">
-        <v>84.59999999999999</v>
+        <v>33.3</v>
       </c>
       <c r="F3">
-        <v>1.43</v>
+        <v>-0.33</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K3">
-        <v>35.5</v>
+        <v>30.7</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>99.95</v>
+        <v>78.72</v>
       </c>
       <c r="E4">
-        <v>47.6</v>
+        <v>52.1</v>
       </c>
       <c r="F4">
-        <v>-0.92</v>
+        <v>-2.2</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J4">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K4">
-        <v>34.5</v>
+        <v>28.7</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,19 +654,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>73.23999999999999</v>
+        <v>97.12</v>
       </c>
       <c r="E5">
-        <v>41.5</v>
+        <v>32.6</v>
       </c>
       <c r="F5">
-        <v>-2.66</v>
+        <v>-1.28</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I5">
         <v>53</v>
@@ -675,7 +675,7 @@
         <v>43</v>
       </c>
       <c r="K5">
-        <v>33.3</v>
+        <v>25.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -534,7 +534,7 @@
         <v>30</v>
       </c>
       <c r="K2">
-        <v>33.5</v>
+        <v>32.2</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -581,7 +581,7 @@
         <v>33</v>
       </c>
       <c r="K3">
-        <v>30.7</v>
+        <v>29.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -628,7 +628,7 @@
         <v>43</v>
       </c>
       <c r="K4">
-        <v>28.7</v>
+        <v>27.4</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>43</v>
       </c>
       <c r="K5">
-        <v>25.5</v>
+        <v>24.2</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
@@ -94,7 +94,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -513,13 +513,13 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>286.48</v>
+        <v>285.17</v>
       </c>
       <c r="E2">
-        <v>44.2</v>
+        <v>48.4</v>
       </c>
       <c r="F2">
-        <v>-2.32</v>
+        <v>-2.56</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -528,13 +528,13 @@
         <v>43</v>
       </c>
       <c r="I2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K2">
-        <v>32.2</v>
+        <v>44.7</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>71.83</v>
+        <v>70.77</v>
       </c>
       <c r="E3">
-        <v>33.3</v>
+        <v>25.9</v>
       </c>
       <c r="F3">
-        <v>-0.33</v>
+        <v>-3.37</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="H3">
+        <v>60</v>
+      </c>
+      <c r="I3">
         <v>56</v>
       </c>
-      <c r="I3">
-        <v>66</v>
-      </c>
       <c r="J3">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K3">
-        <v>29.4</v>
+        <v>35.1</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>78.72</v>
+        <v>77.62</v>
       </c>
       <c r="E4">
-        <v>52.1</v>
+        <v>41.5</v>
       </c>
       <c r="F4">
-        <v>-2.2</v>
+        <v>-4.31</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I4">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J4">
         <v>43</v>
       </c>
       <c r="K4">
-        <v>27.4</v>
+        <v>32.9</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>97.12</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="E5">
-        <v>32.6</v>
+        <v>30.4</v>
       </c>
       <c r="F5">
-        <v>-1.28</v>
+        <v>-4.02</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J5">
         <v>43</v>
       </c>
       <c r="K5">
-        <v>24.2</v>
+        <v>28.1</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
@@ -70,31 +70,31 @@
     <t>MetLife, Inc.</t>
   </si>
   <si>
+    <t>Prudential Financial, Inc.</t>
+  </si>
+  <si>
     <t>American International Group, I</t>
   </si>
   <si>
-    <t>Prudential Financial, Inc.</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
     <t>MET</t>
   </si>
   <si>
+    <t>PRU</t>
+  </si>
+  <si>
     <t>AIG</t>
   </si>
   <si>
-    <t>PRU</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>285.17</v>
+        <v>282.34</v>
       </c>
       <c r="E2">
-        <v>48.4</v>
+        <v>46.8</v>
       </c>
       <c r="F2">
-        <v>-2.56</v>
+        <v>-1.62</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I2">
         <v>50</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>44.7</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>70.77</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E3">
-        <v>25.9</v>
+        <v>22.6</v>
       </c>
       <c r="F3">
-        <v>-3.37</v>
+        <v>-2.85</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>35.1</v>
+        <v>37.2</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>77.62</v>
+        <v>95.47</v>
       </c>
       <c r="E4">
-        <v>41.5</v>
+        <v>25.5</v>
       </c>
       <c r="F4">
-        <v>-4.31</v>
+        <v>-3.32</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I4">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K4">
-        <v>32.9</v>
+        <v>37.2</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>95.93000000000001</v>
+        <v>78.05</v>
       </c>
       <c r="E5">
-        <v>30.4</v>
+        <v>41.7</v>
       </c>
       <c r="F5">
-        <v>-4.02</v>
+        <v>-1.28</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J5">
         <v>43</v>
       </c>
       <c r="K5">
-        <v>28.1</v>
+        <v>33.4</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,31 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
+    <t>Prudential Financial, Inc.</t>
+  </si>
+  <si>
+    <t>American International Group, I</t>
+  </si>
+  <si>
     <t>MetLife, Inc.</t>
   </si>
   <si>
-    <t>Prudential Financial, Inc.</t>
-  </si>
-  <si>
-    <t>American International Group, I</t>
-  </si>
-  <si>
     <t>UNH</t>
   </si>
   <si>
+    <t>PRU</t>
+  </si>
+  <si>
+    <t>AIG</t>
+  </si>
+  <si>
     <t>MET</t>
-  </si>
-  <si>
-    <t>PRU</t>
-  </si>
-  <si>
-    <t>AIG</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>282.34</v>
+        <v>285.25</v>
       </c>
       <c r="E2">
-        <v>46.8</v>
+        <v>47.9</v>
       </c>
       <c r="F2">
-        <v>-1.62</v>
+        <v>-1.54</v>
       </c>
       <c r="G2">
         <v>40</v>
       </c>
       <c r="H2">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I2">
         <v>50</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K2">
-        <v>45</v>
+        <v>44.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>70.59999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="E3">
-        <v>22.6</v>
+        <v>27.1</v>
       </c>
       <c r="F3">
-        <v>-2.85</v>
+        <v>-3.9</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K3">
-        <v>37.2</v>
+        <v>33.9</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>95.47</v>
+        <v>77.97</v>
       </c>
       <c r="E4">
-        <v>25.5</v>
+        <v>42.4</v>
       </c>
       <c r="F4">
-        <v>-3.32</v>
+        <v>-0.42</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I4">
+        <v>36</v>
+      </c>
+      <c r="J4">
         <v>53</v>
       </c>
-      <c r="J4">
-        <v>46</v>
-      </c>
       <c r="K4">
-        <v>37.2</v>
+        <v>32.9</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -654,28 +654,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>78.05</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="E5">
-        <v>41.7</v>
+        <v>23.3</v>
       </c>
       <c r="F5">
-        <v>-1.28</v>
+        <v>-4.58</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J5">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K5">
-        <v>33.4</v>
+        <v>32.7</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>날짜</t>
   </si>
@@ -61,40 +61,43 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>American International Group, I</t>
+  </si>
+  <si>
+    <t>Prudential Financial, Inc.</t>
+  </si>
+  <si>
+    <t>MetLife, Inc.</t>
   </si>
   <si>
     <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
-    <t>Prudential Financial, Inc.</t>
-  </si>
-  <si>
-    <t>American International Group, I</t>
-  </si>
-  <si>
-    <t>MetLife, Inc.</t>
+    <t>AIG</t>
+  </si>
+  <si>
+    <t>PRU</t>
+  </si>
+  <si>
+    <t>MET</t>
   </si>
   <si>
     <t>UNH</t>
   </si>
   <si>
-    <t>PRU</t>
-  </si>
-  <si>
-    <t>AIG</t>
-  </si>
-  <si>
-    <t>MET</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -513,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>285.25</v>
+        <v>76.17</v>
       </c>
       <c r="E2">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="F2">
-        <v>-1.54</v>
+        <v>2.86</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="K2">
-        <v>44.5</v>
+        <v>62</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,10 +546,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -560,40 +563,40 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>94.94</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E3">
-        <v>27.1</v>
+        <v>61.7</v>
       </c>
       <c r="F3">
-        <v>-3.9</v>
+        <v>3.09</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I3">
         <v>46</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K3">
-        <v>33.9</v>
+        <v>56.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -607,40 +610,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>77.97</v>
+        <v>71.2</v>
       </c>
       <c r="E4">
-        <v>42.4</v>
+        <v>59.8</v>
       </c>
       <c r="F4">
-        <v>-0.42</v>
+        <v>4.29</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I4">
         <v>36</v>
       </c>
       <c r="J4">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="K4">
-        <v>32.9</v>
+        <v>52.4</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -654,40 +657,40 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>69.95999999999999</v>
+        <v>307.73</v>
       </c>
       <c r="E5">
-        <v>23.3</v>
+        <v>62.2</v>
       </c>
       <c r="F5">
-        <v>-4.58</v>
+        <v>17.55</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>32.7</v>
+        <v>49.4</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
   </si>
   <si>
     <t>American International Group, I</t>
@@ -70,24 +70,24 @@
     <t>Prudential Financial, Inc.</t>
   </si>
   <si>
+    <t>UnitedHealth Group Incorporated</t>
+  </si>
+  <si>
     <t>MetLife, Inc.</t>
   </si>
   <si>
-    <t>UnitedHealth Group Incorporated</t>
-  </si>
-  <si>
     <t>AIG</t>
   </si>
   <si>
     <t>PRU</t>
   </si>
   <si>
+    <t>UNH</t>
+  </si>
+  <si>
     <t>MET</t>
   </si>
   <si>
-    <t>UNH</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
@@ -97,7 +97,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -516,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>76.17</v>
+        <v>77.69</v>
       </c>
       <c r="E2">
         <v>48.1</v>
       </c>
       <c r="F2">
-        <v>2.86</v>
+        <v>5.29</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -563,13 +563,13 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>97.40000000000001</v>
+        <v>100.16</v>
       </c>
       <c r="E3">
-        <v>61.7</v>
+        <v>50.9</v>
       </c>
       <c r="F3">
-        <v>3.09</v>
+        <v>3.88</v>
       </c>
       <c r="G3">
         <v>60</v>
@@ -578,13 +578,13 @@
         <v>53</v>
       </c>
       <c r="I3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>56.4</v>
+        <v>55.7</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -593,7 +593,7 @@
         <v>26</v>
       </c>
       <c r="N3">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -610,28 +610,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>71.2</v>
+        <v>367.28</v>
       </c>
       <c r="E4">
-        <v>59.8</v>
+        <v>85.7</v>
       </c>
       <c r="F4">
-        <v>4.29</v>
+        <v>-0.93</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K4">
-        <v>52.4</v>
+        <v>54.9</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="N4">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -657,28 +657,28 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>307.73</v>
+        <v>80.16</v>
       </c>
       <c r="E5">
-        <v>62.2</v>
+        <v>65.8</v>
       </c>
       <c r="F5">
-        <v>17.55</v>
+        <v>1.52</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H5">
+        <v>46</v>
+      </c>
+      <c r="I5">
         <v>43</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>36</v>
       </c>
-      <c r="J5">
-        <v>30</v>
-      </c>
       <c r="K5">
-        <v>49.4</v>
+        <v>52.9</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/헷징_보험_분석.xlsx
+++ b/DECISION/헷징_보험_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>날짜</t>
   </si>
@@ -61,43 +61,40 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>Prudential Financial, Inc.</t>
+  </si>
+  <si>
+    <t>MetLife, Inc.</t>
+  </si>
+  <si>
+    <t>UnitedHealth Group Incorporated</t>
   </si>
   <si>
     <t>American International Group, I</t>
   </si>
   <si>
-    <t>Prudential Financial, Inc.</t>
-  </si>
-  <si>
-    <t>UnitedHealth Group Incorporated</t>
-  </si>
-  <si>
-    <t>MetLife, Inc.</t>
+    <t>PRU</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>UNH</t>
   </si>
   <si>
     <t>AIG</t>
   </si>
   <si>
-    <t>PRU</t>
-  </si>
-  <si>
-    <t>UNH</t>
-  </si>
-  <si>
-    <t>MET</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>📈 매수 관찰 구간입니다.</t>
-  </si>
-  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -516,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>77.69</v>
+        <v>104.62</v>
       </c>
       <c r="E2">
-        <v>48.1</v>
+        <v>62.5</v>
       </c>
       <c r="F2">
-        <v>5.29</v>
+        <v>3.95</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>62.1</v>
+        <v>38.9</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,10 +543,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -563,40 +560,40 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>100.16</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E3">
-        <v>50.9</v>
+        <v>65.2</v>
       </c>
       <c r="F3">
-        <v>3.88</v>
+        <v>2.18</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I3">
+        <v>46</v>
+      </c>
+      <c r="J3">
         <v>50</v>
       </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
       <c r="K3">
-        <v>55.7</v>
+        <v>37.3</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <v>13.11002090356014</v>
+      </c>
+      <c r="O3" t="s">
         <v>26</v>
-      </c>
-      <c r="N3">
-        <v>59.14876667115259</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -610,40 +607,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>367.28</v>
+        <v>399.47</v>
       </c>
       <c r="E4">
-        <v>85.7</v>
+        <v>54.3</v>
       </c>
       <c r="F4">
-        <v>-0.93</v>
+        <v>5.04</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="J4">
         <v>33</v>
       </c>
       <c r="K4">
-        <v>54.9</v>
+        <v>27.9</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
+        <v>13.11002090356014</v>
+      </c>
+      <c r="O4" t="s">
         <v>26</v>
-      </c>
-      <c r="N4">
-        <v>59.14876667115259</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -657,40 +654,40 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>80.16</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="E5">
-        <v>65.8</v>
+        <v>47.8</v>
       </c>
       <c r="F5">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J5">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K5">
-        <v>52.9</v>
+        <v>27.3</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5">
+        <v>13.11002090356014</v>
+      </c>
+      <c r="O5" t="s">
         <v>26</v>
-      </c>
-      <c r="N5">
-        <v>59.14876667115259</v>
-      </c>
-      <c r="O5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
